--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487867_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487867_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3791</v>
+        <v>4.3996</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1502</v>
+        <v>1.9359</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2289</v>
+        <v>2.4637</v>
       </c>
       <c r="G2" t="n">
         <v>-0.0597</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3118</v>
+        <v>0.3324</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.2829</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3804</v>
+        <v>0.6153</v>
       </c>
       <c r="V2" t="n">
         <v>3.5026</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9403</v>
+        <v>3.711</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8546</v>
+        <v>3.3904</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0857</v>
+        <v>0.3206</v>
       </c>
       <c r="G3" t="n">
         <v>3.5284</v>
@@ -688,13 +688,13 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.0171</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8482</v>
+        <v>-0.3124</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0946</v>
+        <v>0.3295</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2914</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1692</v>
+        <v>1.3017</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2014</v>
+        <v>3.4513</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0322</v>
+        <v>-2.1497</v>
       </c>
       <c r="G4" t="n">
         <v>1.7595</v>
@@ -766,13 +766,13 @@
         <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7665999999999999</v>
+        <v>-0.101</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.1567</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1402</v>
+        <v>-0.2577</v>
       </c>
       <c r="V4" t="n">
         <v>-1.3975</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>A. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9245</v>
+        <v>1.1258</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6723</v>
+        <v>1.3102</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5968</v>
+        <v>-0.1844</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8732</v>
+        <v>1.4671</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0765</v>
+        <v>-0.0703</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2033</v>
+        <v>1.5373</v>
       </c>
       <c r="J5" t="n">
-        <v>2.257</v>
+        <v>1.2916</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1786</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0784</v>
+        <v>1.2148</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3838</v>
+        <v>0.1755</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1022</v>
+        <v>-0.147</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2817</v>
+        <v>0.3225</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.0812</v>
+        <v>0.4162</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0086</v>
+        <v>0.41</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1924</v>
+        <v>0.0186</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8162</v>
+        <v>0.3915</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1238</v>
+        <v>-1.1675</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1238</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. OROZCO DOMINGUEZ</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6766</v>
+        <v>0.6808</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0959</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4192</v>
+        <v>1.5675</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4671</v>
+        <v>1.8732</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0703</v>
+        <v>2.0765</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5373</v>
+        <v>-0.2033</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2916</v>
+        <v>2.257</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07679999999999999</v>
+        <v>2.1786</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2148</v>
+        <v>0.0784</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1755</v>
+        <v>-0.3838</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.147</v>
+        <v>-0.1022</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3225</v>
+        <v>-0.2817</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4162</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0391</v>
+        <v>0.765</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1957</v>
+        <v>-0.0219</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1566</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1675</v>
+        <v>0.1238</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1675</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5627</v>
+        <v>0.5436</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1333</v>
+        <v>1.0262</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5707</v>
+        <v>-0.4826</v>
       </c>
       <c r="G7" t="n">
         <v>0.0573</v>
@@ -1000,13 +1000,13 @@
         <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>0.214</v>
+        <v>0.1949</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2577</v>
+        <v>0.1505</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0437</v>
+        <v>0.0444</v>
       </c>
       <c r="V7" t="n">
         <v>0.7076</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>J. SIENCHE GUEMETA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1111</v>
+        <v>0.1464</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8812</v>
+        <v>0.361</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9923</v>
+        <v>-0.2146</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2501</v>
+        <v>0.3046</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1217</v>
+        <v>0.049</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.3718</v>
+        <v>0.2555</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0947</v>
+        <v>0.2842</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2812</v>
+        <v>0.245</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.3759</v>
+        <v>0.0392</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1554</v>
+        <v>0.0203</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1595</v>
+        <v>-0.196</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0041</v>
+        <v>0.2164</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6244</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7993</v>
+        <v>0.153</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9134</v>
+        <v>-0.1771</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7127</v>
+        <v>0.3301</v>
       </c>
       <c r="V8" t="n">
         <v>0.9376</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1675</v>
+        <v>2.3351</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.23</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SIENCHE GUEMETA</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.156</v>
+        <v>-0.1165</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1466</v>
+        <v>-2.3454</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3026</v>
+        <v>2.2289</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3046</v>
+        <v>-2.2501</v>
       </c>
       <c r="H9" t="n">
-        <v>0.049</v>
+        <v>1.1217</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2555</v>
+        <v>-3.3718</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2842</v>
+        <v>-2.0947</v>
       </c>
       <c r="K9" t="n">
-        <v>0.245</v>
+        <v>1.2812</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0392</v>
+        <v>-3.3759</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0203</v>
+        <v>-0.1554</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.196</v>
+        <v>-0.1595</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2164</v>
+        <v>0.0041</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1494</v>
+        <v>0.5717</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3915</v>
+        <v>-0.3776</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2421</v>
+        <v>0.9493</v>
       </c>
       <c r="V9" t="n">
         <v>0.9376</v>
       </c>
       <c r="W9" t="n">
-        <v>2.3351</v>
+        <v>1.1675</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3975</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6735</v>
+        <v>-1.9028</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8774</v>
+        <v>-2.3416</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2039</v>
+        <v>0.4388</v>
       </c>
       <c r="G10" t="n">
         <v>1.8755</v>
@@ -1234,13 +1234,13 @@
         <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0921</v>
+        <v>-0.3215</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0439</v>
+        <v>-0.5081</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0482</v>
+        <v>0.1866</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1675</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9781</v>
+        <v>-3.9338</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7266</v>
+        <v>-5.4767</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7485</v>
+        <v>1.5429</v>
       </c>
       <c r="G11" t="n">
         <v>0.7519</v>
@@ -1312,13 +1312,13 @@
         <v>0.8325</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9318</v>
+        <v>0.9762</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.1567</v>
       </c>
       <c r="U11" t="n">
-        <v>1.025</v>
+        <v>0.8195</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2914</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9559</v>
+        <v>5.955800000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4244999999999992</v>
+        <v>0.4246999999999987</v>
       </c>
       <c r="F12" t="n">
-        <v>5.5314</v>
+        <v>5.531099999999999</v>
       </c>
       <c r="G12" t="n">
         <v>9.307700000000001</v>
@@ -1369,7 +1369,7 @@
         <v>11.085</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3878000000000001</v>
+        <v>-0.3877999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-1.3896</v>
@@ -1378,7 +1378,7 @@
         <v>-1.7775</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3878</v>
+        <v>0.3877999999999999</v>
       </c>
       <c r="P12" t="n">
         <v>-6.243499999999999</v>
@@ -1390,13 +1390,13 @@
         <v>11.4465</v>
       </c>
       <c r="S12" t="n">
-        <v>2.997999999999999</v>
+        <v>2.9978</v>
       </c>
       <c r="T12" t="n">
         <v>-1.1975</v>
       </c>
       <c r="U12" t="n">
-        <v>4.1955</v>
+        <v>4.1953</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1061000000000003</v>
@@ -1405,7 +1405,7 @@
         <v>8.614999999999998</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.720999999999998</v>
+        <v>-8.721</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9079</v>
+        <v>4.3072</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7033</v>
+        <v>3.1319</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2046</v>
+        <v>1.1753</v>
       </c>
       <c r="G13" t="n">
         <v>1.7507</v>
@@ -1468,13 +1468,13 @@
         <v>2.4974</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0478</v>
+        <v>-0.6485</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1091</v>
+        <v>-0.6805</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0614</v>
+        <v>0.032</v>
       </c>
       <c r="V13" t="n">
         <v>0.7076</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8681</v>
+        <v>2.844</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5395</v>
+        <v>3.021</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3285</v>
+        <v>-0.177</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5526</v>
+        <v>-0.8683</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.9813</v>
+        <v>-2.0301</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4287</v>
+        <v>1.1618</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9499</v>
+        <v>0.8138</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2951</v>
+        <v>-0.3438</v>
       </c>
       <c r="L14" t="n">
-        <v>1.245</v>
+        <v>1.1577</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5025</v>
+        <v>-1.6821</v>
       </c>
       <c r="N14" t="n">
         <v>-1.6862</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1837</v>
+        <v>0.0041</v>
       </c>
       <c r="P14" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2893</v>
+        <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4313</v>
+        <v>-0.4365</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3948</v>
+        <v>-0.4848</v>
       </c>
       <c r="U14" t="n">
-        <v>0.826</v>
+        <v>0.0483</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7407</v>
+        <v>3.7325</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0249</v>
+        <v>3.7325</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2392</v>
+        <v>2.5642</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5924</v>
+        <v>2.6467</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3531</v>
+        <v>-0.0825</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8683</v>
+        <v>-0.5526</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.0301</v>
+        <v>-1.9813</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1618</v>
+        <v>1.4287</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8138</v>
+        <v>0.9499</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3438</v>
+        <v>-0.2951</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1577</v>
+        <v>1.245</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6821</v>
+        <v>-1.5025</v>
       </c>
       <c r="N15" t="n">
         <v>-1.6862</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0041</v>
+        <v>0.1837</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4568</v>
+        <v>2.2893</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0413</v>
+        <v>0.1274</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9134</v>
+        <v>-0.2876</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1278</v>
+        <v>0.415</v>
       </c>
       <c r="V15" t="n">
-        <v>3.7325</v>
+        <v>1.7407</v>
       </c>
       <c r="W15" t="n">
-        <v>3.7325</v>
+        <v>3.0249</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2843</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3685</v>
+        <v>1.0851</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5522</v>
+        <v>0.445</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8163</v>
+        <v>0.6402</v>
       </c>
       <c r="G16" t="n">
         <v>1.9265</v>
@@ -1702,13 +1702,13 @@
         <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7679</v>
+        <v>0.4846</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1924</v>
+        <v>0.0853</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5755</v>
+        <v>0.3993</v>
       </c>
       <c r="V16" t="n">
         <v>0.1309</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2005</v>
+        <v>-0.2116</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3687</v>
+        <v>-0.1315</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1682</v>
+        <v>-0.0801</v>
       </c>
       <c r="G17" t="n">
         <v>0.2409</v>
@@ -1780,13 +1780,13 @@
         <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>2.149</v>
+        <v>0.7369</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3355</v>
+        <v>0.8354</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1866</v>
+        <v>-0.0985</v>
       </c>
       <c r="V17" t="n">
         <v>-1.3975</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9169</v>
+        <v>-0.8582</v>
       </c>
       <c r="E18" t="n">
         <v>-1.2824</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3655</v>
+        <v>0.4242</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2788</v>
@@ -1858,13 +1858,13 @@
         <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2218</v>
+        <v>-0.1631</v>
       </c>
       <c r="T18" t="n">
         <v>-0.261</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0391</v>
+        <v>0.0979</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2106</v>
+        <v>-1.1137</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4495</v>
+        <v>-2.2352</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2389</v>
+        <v>1.1215</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3784</v>
@@ -1936,13 +1936,13 @@
         <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1683</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4567</v>
+        <v>-0.2424</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2884</v>
+        <v>0.171</v>
       </c>
       <c r="V19" t="n">
         <v>0.9199000000000001</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.061</v>
+        <v>-1.788</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9642</v>
+        <v>-2.7499</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9032</v>
+        <v>0.9619</v>
       </c>
       <c r="G20" t="n">
         <v>-3.0879</v>
@@ -2014,13 +2014,13 @@
         <v>2.2893</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2624</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9134</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.349</v>
+        <v>-0.2903</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1462</v>
+        <v>-1.9612</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6488</v>
+        <v>-0.4345</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4974</v>
+        <v>-1.5267</v>
       </c>
       <c r="G21" t="n">
         <v>0.8843</v>
@@ -2092,13 +2092,13 @@
         <v>2.0812</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5787</v>
+        <v>-0.3937</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7829</v>
+        <v>-0.5686</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2042</v>
+        <v>0.1749</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4518</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1783</v>
+        <v>-3.9728</v>
       </c>
       <c r="E22" t="n">
         <v>-3.2669</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9114</v>
+        <v>-0.7059</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1649</v>
@@ -2170,13 +2170,13 @@
         <v>2.2893</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2703</v>
+        <v>-1.0647</v>
       </c>
       <c r="T22" t="n">
         <v>-0.9786</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2916</v>
+        <v>-0.0861</v>
       </c>
       <c r="V22" t="n">
         <v>-1.9919</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.0271</v>
+        <v>-6.8509</v>
       </c>
       <c r="E23" t="n">
         <v>-4.6755</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3515</v>
+        <v>-2.1753</v>
       </c>
       <c r="G23" t="n">
         <v>-4.7792</v>
@@ -2248,13 +2248,13 @@
         <v>0.8325</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.5793</v>
       </c>
       <c r="T23" t="n">
         <v>-0.9134</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1579</v>
+        <v>0.3341</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2843</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.955900000000001</v>
+        <v>-5.9559</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.531200000000002</v>
+        <v>-5.5313</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4245999999999999</v>
+        <v>-0.4243999999999997</v>
       </c>
       <c r="G24" t="n">
         <v>-9.307700000000001</v>
@@ -2326,19 +2326,19 @@
         <v>17.6901</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.9979</v>
+        <v>-2.9977</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.1954</v>
+        <v>-4.1953</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1975</v>
+        <v>1.1976</v>
       </c>
       <c r="V24" t="n">
         <v>0.1061000000000003</v>
       </c>
       <c r="W24" t="n">
-        <v>8.721</v>
+        <v>8.721000000000002</v>
       </c>
       <c r="X24" t="n">
         <v>-8.615</v>
